--- a/artfynd/A 59728-2021 artfynd.xlsx
+++ b/artfynd/A 59728-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59728-2021 artfynd.xlsx
+++ b/artfynd/A 59728-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1903,10 +1903,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96928323</v>
+        <v>96928313</v>
       </c>
       <c r="B12" t="n">
-        <v>95511</v>
+        <v>98520</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221944</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520692.3348301785</v>
+        <v>520869.8039987626</v>
       </c>
       <c r="R12" t="n">
-        <v>6706205.516838319</v>
+        <v>6706074.952538479</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2020,10 +2020,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96928313</v>
+        <v>104316288</v>
       </c>
       <c r="B13" t="n">
-        <v>98520</v>
+        <v>5113</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2036,41 +2036,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Plättbacken, Dlr</t>
+          <t>Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520869.8039987626</v>
+        <v>520807.8065093574</v>
       </c>
       <c r="R13" t="n">
-        <v>6706074.952538479</v>
+        <v>6706125.849586501</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2094,7 +2096,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2104,7 +2106,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2118,7 +2120,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2130,17 +2131,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jakob Wallin, Matilda Elgerud</t>
+          <t>Jakob Wallin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104316288</v>
+        <v>112389296</v>
       </c>
       <c r="B14" t="n">
-        <v>5113</v>
+        <v>94409</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2149,47 +2150,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Borlänge, Dlr</t>
+          <t>Paradiset, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520807.8065093574</v>
+        <v>520702</v>
       </c>
       <c r="R14" t="n">
-        <v>6706125.849586501</v>
+        <v>6706232</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2213,22 +2209,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2243,22 +2239,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jakob Wallin</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jakob Wallin</t>
+          <t>Uno Skog, Holger Martinussen, Anton Björk</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112389296</v>
+        <v>112389778</v>
       </c>
       <c r="B15" t="n">
-        <v>94409</v>
+        <v>96844</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2267,39 +2263,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Paradiset, Dlr</t>
+          <t>Övre Tjärna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520702</v>
+        <v>520924</v>
       </c>
       <c r="R15" t="n">
-        <v>6706232</v>
+        <v>6706050</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2329,46 +2336,37 @@
           <t>2023-09-29</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-09-29</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Holger Martinussen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Uno Skog, Holger Martinussen, Anton Björk</t>
+          <t>Holger Martinussen, Uno Skog, Anton Björk</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112389778</v>
+        <v>112388168</v>
       </c>
       <c r="B16" t="n">
         <v>96844</v>
@@ -2403,7 +2401,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2420,10 +2418,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520924</v>
+        <v>520808</v>
       </c>
       <c r="R16" t="n">
-        <v>6706050</v>
+        <v>6706139</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2483,10 +2481,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112388168</v>
+        <v>112435727</v>
       </c>
       <c r="B17" t="n">
-        <v>96844</v>
+        <v>89653</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2495,53 +2493,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Övre Tjärna, Dlr</t>
+          <t>Plättbacken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520808</v>
+        <v>520887</v>
       </c>
       <c r="R17" t="n">
-        <v>6706139</v>
+        <v>6706018</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2579,29 +2565,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Holger Martinussen</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Holger Martinussen, Uno Skog, Anton Björk</t>
+          <t>Anton Björk, Uno Skog, Holger Martinussen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112435727</v>
+        <v>112435720</v>
       </c>
       <c r="B18" t="n">
-        <v>89653</v>
+        <v>83599</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2614,21 +2599,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>241</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2638,13 +2623,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520887</v>
+        <v>520679</v>
       </c>
       <c r="R18" t="n">
-        <v>6706018</v>
+        <v>6706241</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2700,10 +2685,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112435720</v>
+        <v>112388247</v>
       </c>
       <c r="B19" t="n">
-        <v>83599</v>
+        <v>96853</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2712,38 +2697,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>241</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Plättbacken, Dlr</t>
+          <t>Paradiset, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520679</v>
+        <v>520819</v>
       </c>
       <c r="R19" t="n">
-        <v>6706241</v>
+        <v>6706134</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2773,9 +2759,19 @@
           <t>2023-09-29</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2790,22 +2786,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anton Björk, Uno Skog, Holger Martinussen</t>
+          <t>Uno Skog, Holger Martinussen, Anton Björk</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112388247</v>
+        <v>112389655</v>
       </c>
       <c r="B20" t="n">
-        <v>96853</v>
+        <v>90943</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2814,25 +2810,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2843,10 +2839,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520819</v>
+        <v>520873</v>
       </c>
       <c r="R20" t="n">
-        <v>6706134</v>
+        <v>6706060</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2878,7 +2874,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2888,7 +2884,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2915,10 +2911,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112389655</v>
+        <v>112389127</v>
       </c>
       <c r="B21" t="n">
-        <v>90943</v>
+        <v>96853</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2927,25 +2923,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2956,10 +2952,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520873</v>
+        <v>520688</v>
       </c>
       <c r="R21" t="n">
-        <v>6706060</v>
+        <v>6706226</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2991,7 +2987,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3001,7 +2997,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3028,7 +3024,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112389127</v>
+        <v>112388456</v>
       </c>
       <c r="B22" t="n">
         <v>96853</v>
@@ -3069,10 +3065,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520688</v>
+        <v>520759</v>
       </c>
       <c r="R22" t="n">
-        <v>6706226</v>
+        <v>6706151</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3104,7 +3100,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3114,7 +3110,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3138,119 +3134,6 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>112388456</v>
-      </c>
-      <c r="B23" t="n">
-        <v>96853</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Paradiset, Dlr</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>520759</v>
-      </c>
-      <c r="R23" t="n">
-        <v>6706151</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Borlänge</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Stora Tuna</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2023-09-29</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2023-09-29</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Uno Skog</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Uno Skog, Holger Martinussen, Anton Björk</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59728-2021 artfynd.xlsx
+++ b/artfynd/A 59728-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96928320</v>
+        <v>112389296</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Plättbacken, Dlr</t>
+          <t>Paradiset, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520735.4704290726</v>
+        <v>520702</v>
       </c>
       <c r="R2" t="n">
-        <v>6706172.252320063</v>
+        <v>6706232</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,22 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,80 +765,66 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jakob Wallin</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jakob Wallin, Matilda Elgerud</t>
+          <t>Uno Skog, Holger Martinussen, Anton Björk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96928311</v>
+        <v>112435720</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85534</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>241</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Shear</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>plättbacken, Dlr</t>
+          <t>Plättbacken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520984.0592507967</v>
+        <v>520679</v>
       </c>
       <c r="R3" t="n">
-        <v>6706036.186671116</v>
+        <v>6706242</v>
       </c>
       <c r="S3" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +848,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,80 +862,66 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jakob Wallin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jakob Wallin, Matilda Elgerud</t>
+          <t>Anton Björk, Uno Skog, Holger Martinussen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96928315</v>
+        <v>112435727</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Plättbacken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520819.4915988598</v>
+        <v>520887</v>
       </c>
       <c r="R4" t="n">
-        <v>6706154.007737498</v>
+        <v>6706018</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,27 +945,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>1 blommande</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,34 +959,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jakob Wallin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jakob Wallin, Matilda Elgerud</t>
+          <t>Anton Björk, Uno Skog, Holger Martinussen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96928322</v>
+        <v>96928317</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,31 +988,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1965</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Citronporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antrodiella citrinella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä &amp; Ryvarden</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1091,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520708.1639998886</v>
+        <v>520799</v>
       </c>
       <c r="R5" t="n">
-        <v>6706199.693643033</v>
+        <v>6706118</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,19 +1056,14 @@
           <t>2021-10-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-10-27</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2-3 dm lång fruktkropp utan hatt på granlåga utan synliga klibbtickor. Mycket klibbticka på närliggande granlågor. Mikroskoperad/validerad av Jan Olof Hermansson.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,6 +1075,11 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1164,61 +1096,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96928317</v>
+        <v>112388540</v>
       </c>
       <c r="B6" t="n">
-        <v>90014</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1965</v>
+        <v>2809</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Citronporing</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Antrodiella citrinella</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Ryvarden</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Plättbacken, Dlr</t>
+          <t>Paradiset, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520798.9667800993</v>
+        <v>520683</v>
       </c>
       <c r="R6" t="n">
-        <v>6706117.913543107</v>
+        <v>6706163</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,27 +1162,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2-3 dm lång fruktkropp utan hatt på granlåga utan synliga klibbtickor. Mycket klibbticka på närliggande granlågor. Mikroskoperad/validerad av Jan Olof Hermansson.</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,82 +1186,64 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jakob Wallin</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jakob Wallin, Matilda Elgerud</t>
+          <t>Uno Skog, Holger Martinussen, Anton Björk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96928314</v>
+        <v>112388519</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Plättbacken, Dlr</t>
+          <t>Paradiset, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520838.7086794741</v>
+        <v>520702</v>
       </c>
       <c r="R7" t="n">
-        <v>6706074.280456046</v>
+        <v>6706153</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1376,22 +1270,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,77 +1294,73 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jakob Wallin</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jakob Wallin, Matilda Elgerud</t>
+          <t>Uno Skog, Holger Martinussen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96928316</v>
+        <v>112388509</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Plättbacken, Dlr</t>
+          <t>Paradiset, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520798.9667800993</v>
+        <v>520702</v>
       </c>
       <c r="R8" t="n">
-        <v>6706117.913543107</v>
+        <v>6706153</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1497,22 +1387,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,77 +1411,64 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jakob Wallin</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jakob Wallin, Matilda Elgerud</t>
+          <t>Uno Skog, Holger Martinussen, Anton Björk</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96928321</v>
+        <v>112389655</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Plättbacken, Dlr</t>
+          <t>Paradiset, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520723.5504311257</v>
+        <v>520873</v>
       </c>
       <c r="R9" t="n">
-        <v>6706184.99727731</v>
+        <v>6706060</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1618,22 +1495,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1642,80 +1519,72 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jakob Wallin</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jakob Wallin, Matilda Elgerud</t>
+          <t>Uno Skog, Holger Martinussen, Anton Björk</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96928319</v>
+        <v>104316288</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Plättbacken, Dlr</t>
+          <t>Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520751.8330007689</v>
+        <v>520808</v>
       </c>
       <c r="R10" t="n">
-        <v>6706159.532837916</v>
+        <v>6706126</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1739,22 +1608,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1763,7 +1622,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1775,22 +1633,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jakob Wallin, Matilda Elgerud</t>
+          <t>Jakob Wallin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96928318</v>
+        <v>96928311</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1670,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -1826,17 +1679,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Plättbacken, Dlr</t>
+          <t>plättbacken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520739.5294794704</v>
+        <v>520984</v>
       </c>
       <c r="R11" t="n">
-        <v>6706153.055610015</v>
+        <v>6706036</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1863,19 +1716,9 @@
           <t>2021-10-27</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-10-27</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1903,40 +1746,39 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96928323</v>
+        <v>96928314</v>
       </c>
       <c r="B12" t="n">
-        <v>95511</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221944</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1947,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520692.3348301785</v>
+        <v>520838</v>
       </c>
       <c r="R12" t="n">
-        <v>6706205.516838319</v>
+        <v>6706075</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1980,19 +1822,9 @@
           <t>2021-10-27</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-10-27</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2020,40 +1852,39 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96928313</v>
+        <v>96928315</v>
       </c>
       <c r="B13" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -2064,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520869.8039987626</v>
+        <v>520820</v>
       </c>
       <c r="R13" t="n">
-        <v>6706074.952538479</v>
+        <v>6706154</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2097,19 +1928,14 @@
           <t>2021-10-27</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-10-27</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>1 blommande</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2137,59 +1963,56 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104316288</v>
+        <v>96928316</v>
       </c>
       <c r="B14" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Borlänge, Dlr</t>
+          <t>Plättbacken, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520807.8065093574</v>
+        <v>520799</v>
       </c>
       <c r="R14" t="n">
-        <v>6706125.849586501</v>
+        <v>6706118</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2213,22 +2036,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2237,6 +2050,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2248,58 +2062,60 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jakob Wallin</t>
+          <t>Jakob Wallin, Matilda Elgerud</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112389296</v>
+        <v>96928318</v>
       </c>
       <c r="B15" t="n">
-        <v>94409</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Paradiset, Dlr</t>
+          <t>Plättbacken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520702</v>
+        <v>520740</v>
       </c>
       <c r="R15" t="n">
-        <v>6706232</v>
+        <v>6706153</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2326,22 +2142,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:03</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:03</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2350,33 +2156,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Jakob Wallin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Uno Skog, Holger Martinussen, Anton Björk</t>
+          <t>Jakob Wallin, Matilda Elgerud</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112389778</v>
+        <v>96928319</v>
       </c>
       <c r="B16" t="n">
-        <v>96844</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2406,24 +2208,20 @@
           <t>20</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Övre Tjärna, Dlr</t>
+          <t>Plättbacken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520924</v>
+        <v>520752</v>
       </c>
       <c r="R16" t="n">
-        <v>6706050</v>
+        <v>6706159</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2450,12 +2248,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2471,27 +2269,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Holger Martinussen</t>
+          <t>Jakob Wallin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Holger Martinussen, Uno Skog, Anton Björk</t>
+          <t>Jakob Wallin, Matilda Elgerud</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112388168</v>
+        <v>96928320</v>
       </c>
       <c r="B17" t="n">
-        <v>96844</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2518,27 +2311,23 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Övre Tjärna, Dlr</t>
+          <t>Plättbacken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520808</v>
+        <v>520736</v>
       </c>
       <c r="R17" t="n">
-        <v>6706139</v>
+        <v>6706172</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2565,12 +2354,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2586,65 +2375,68 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Holger Martinussen</t>
+          <t>Jakob Wallin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Holger Martinussen, Uno Skog, Anton Björk</t>
+          <t>Jakob Wallin, Matilda Elgerud</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112435727</v>
+        <v>96928321</v>
       </c>
       <c r="B18" t="n">
-        <v>89653</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Plättbacken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520887</v>
+        <v>520723</v>
       </c>
       <c r="R18" t="n">
-        <v>6706018</v>
+        <v>6706185</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2668,12 +2460,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2682,68 +2474,72 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Jakob Wallin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anton Björk, Uno Skog, Holger Martinussen</t>
+          <t>Jakob Wallin, Matilda Elgerud</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112435720</v>
+        <v>96928322</v>
       </c>
       <c r="B19" t="n">
-        <v>83599</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>241</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Plättbacken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520679</v>
+        <v>520708</v>
       </c>
       <c r="R19" t="n">
-        <v>6706241</v>
+        <v>6706200</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2770,12 +2566,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2784,33 +2580,29 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Jakob Wallin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anton Björk, Uno Skog, Holger Martinussen</t>
+          <t>Jakob Wallin, Matilda Elgerud</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112388247</v>
+        <v>112388168</v>
       </c>
       <c r="B20" t="n">
-        <v>96853</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2835,18 +2627,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Paradiset, Dlr</t>
+          <t>Övre Tjärna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520819</v>
+        <v>520808</v>
       </c>
       <c r="R20" t="n">
-        <v>6706134</v>
+        <v>6706139</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2876,76 +2679,62 @@
           <t>2023-09-29</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>08:46</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-09-29</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>08:46</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Holger Martinussen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Uno Skog, Holger Martinussen, Anton Björk</t>
+          <t>Holger Martinussen, Uno Skog, Anton Björk</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112389655</v>
+        <v>112388247</v>
       </c>
       <c r="B21" t="n">
-        <v>90943</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2956,10 +2745,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520873</v>
+        <v>520819</v>
       </c>
       <c r="R21" t="n">
-        <v>6706060</v>
+        <v>6706134</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2991,7 +2780,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3001,7 +2790,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3028,15 +2817,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112389127</v>
+        <v>112388456</v>
       </c>
       <c r="B22" t="n">
-        <v>96853</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3069,10 +2853,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520688</v>
+        <v>520759</v>
       </c>
       <c r="R22" t="n">
-        <v>6706226</v>
+        <v>6706150</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3104,7 +2888,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3114,7 +2898,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3141,15 +2925,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112388456</v>
+        <v>112389127</v>
       </c>
       <c r="B23" t="n">
-        <v>96853</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3182,10 +2961,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520759</v>
+        <v>520688</v>
       </c>
       <c r="R23" t="n">
-        <v>6706151</v>
+        <v>6706226</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3217,7 +2996,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3227,7 +3006,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3251,6 +3030,528 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>112389778</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Övre Tjärna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>520924</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6706050</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Holger Martinussen</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Holger Martinussen, Uno Skog, Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>112435722</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Plättbacken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>520690</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6706244</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anton Björk, Uno Skog, Holger Martinussen</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>96928323</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Plättbacken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>520692</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6706206</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2021-10-27</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2021-10-27</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jakob Wallin</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jakob Wallin, Matilda Elgerud</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>96928313</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Plättbacken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>520870</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6706075</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2021-10-27</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2021-10-27</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jakob Wallin</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jakob Wallin, Matilda Elgerud</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>112389100</v>
+      </c>
+      <c r="B28" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Övre Tjärna, Övre Tjärna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>520673</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6706193</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Holger Martinussen</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Holger Martinussen, Uno Skog, Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59728-2021 artfynd.xlsx
+++ b/artfynd/A 59728-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112389296</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -877,6 +887,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112435720</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -974,6 +989,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112435727</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1093,6 +1113,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96928317</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112388540</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1309,6 +1339,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112388519</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112388509</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1534,6 +1574,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112389655</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1637,6 +1682,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104316288</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1743,6 +1793,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96928311</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96928314</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1960,6 +2020,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96928315</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2066,6 +2131,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96928316</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2172,6 +2242,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96928318</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2278,6 +2353,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96928319</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96928320</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2490,6 +2575,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96928321</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2596,6 +2686,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96928322</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2706,6 +2801,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112388168</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2814,6 +2914,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112388247</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2922,6 +3027,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112388456</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3030,6 +3140,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112389127</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3140,6 +3255,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112389778</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3250,6 +3370,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112435722</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3348,6 +3473,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96928323</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3450,6 +3580,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96928313</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3552,8 +3687,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112389100</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>